--- a/INSTANCES/instances_xlsx/A_MTN_8/379FL_15A_5.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_8/379FL_15A_5.xlsx
@@ -12071,7 +12071,7 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -12122,7 +12122,7 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -12139,7 +12139,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -12156,7 +12156,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -12173,7 +12173,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -12207,7 +12207,7 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -12241,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>1</v>
